--- a/extenbooks/ES1701.xlsx
+++ b/extenbooks/ES1701.xlsx
@@ -681,7 +681,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B50"/>
+  <dimension ref="A1:B53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -732,7 +732,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Study 8</t>
+          <t>17</t>
         </is>
       </c>
     </row>
@@ -776,7 +776,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1972–1995</t>
+          <t>1972-1995</t>
         </is>
       </c>
     </row>
@@ -834,174 +834,175 @@
     </row>
     <row r="14"/>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Subseries</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>source / role</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>ES1701-A</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Cronin 2001 RPE Table 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>DPR (markdown)</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t># ES1701 — NZ Surplus Share of Total Value (Cronin 2001)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr"/>
-      <c r="B17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr"/>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>**Chapter**: External study (Cronin 2001 RPE Table 2)</t>
-        </is>
-      </c>
+      <c r="B18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>**Status**: book_period_validated</t>
+          <t># ES1701 — NZ Surplus Share of Total Value (Cronin 2001)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>**Period**: [1972, 1995]</t>
-        </is>
-      </c>
+      <c r="B20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>**Units**: share</t>
+          <t>**Chapter**: External study (Cronin 2001 RPE Table 2)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr"/>
-      <c r="B22" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>**Status**: book_period_validated</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>## Definition</t>
+          <t>**Period**: [1972, 1995]</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
-      <c r="B24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>**Units**: share</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr"/>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>From Cronin's RPE Table 2; New Zealand classical national accounts surplus share. Percent.</t>
-        </is>
-      </c>
+      <c r="B25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr"/>
-      <c r="B26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>## Definition</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr"/>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>## Source</t>
-        </is>
-      </c>
+      <c r="B27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr"/>
-      <c r="B28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>From Cronin's RPE Table 2; New Zealand classical national accounts surplus share. Percent.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr"/>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>`data/source/external_studies/Cronin2001_cronin_table2_ratios_1972_1995.csv` (copied from ST2's ExternalSources). Loader: `code/L01_loaders/L01_ES1701_nz_surplus_share_cronin2001.py`. Processor: pass-through (P02). Validator: `code/V03_validators/V03_ES1701_nz_surplus_share_cronin2001.py`.</t>
-        </is>
-      </c>
+      <c r="B29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr"/>
-      <c r="B30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>## Source</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr"/>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>## Validation</t>
-        </is>
-      </c>
+      <c r="B31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr"/>
-      <c r="B32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>`data/source/external_studies/Cronin2001_cronin_table2_ratios_1972_1995.csv` (copied from ST2's ExternalSources). Loader: `code/L01_loaders/L01_ES1701_nz_surplus_share_cronin2001.py`. Processor: pass-through (P02). Validator: `code/V03_validators/V03_ES1701_nz_surplus_share_cronin2001.py`.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr"/>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>V03 PASS against endpoint values verified directly against the source CSV.</t>
-        </is>
-      </c>
+      <c r="B33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr"/>
-      <c r="B34" t="inlineStr"/>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>## Validation</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr"/>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>## Provenance</t>
-        </is>
-      </c>
+      <c r="B35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr"/>
-      <c r="B36" t="inlineStr"/>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>V03 PASS against endpoint values verified directly against the source CSV.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr"/>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>```</t>
-        </is>
-      </c>
+      <c r="B37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
-          <t>data/source/external_studies/Cronin2001_cronin_table2_ratios_1972_1995.csv</t>
+          <t>## Provenance</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr"/>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  -&gt; L01_ES1701 -&gt; data/intermediate/ES1701.csv</t>
-        </is>
-      </c>
+      <c r="B39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
-          <t xml:space="preserve">  -&gt; P02_ES1701 -&gt; data/final/ES1701.csv</t>
+          <t>```</t>
         </is>
       </c>
     </row>
@@ -1009,7 +1010,7 @@
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
-          <t xml:space="preserve">  -&gt; V03_ES1701 -&gt; data/intermediate/validation/ES1701.json</t>
+          <t>data/source/external_studies/Cronin2001_cronin_table2_ratios_1972_1995.csv</t>
         </is>
       </c>
     </row>
@@ -1017,53 +1018,77 @@
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr">
         <is>
-          <t>```</t>
+          <t xml:space="preserve">  -&gt; L01_ES1701 -&gt; data/intermediate/ES1701.csv</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr"/>
-      <c r="B43" t="inlineStr"/>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  -&gt; P02_ES1701 -&gt; data/final/ES1701.csv</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr">
         <is>
-          <t>## Citation</t>
+          <t xml:space="preserve">  -&gt; V03_ES1701 -&gt; data/intermediate/validation/ES1701.json</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr"/>
-      <c r="B45" t="inlineStr"/>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>```</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr"/>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Cronin, Bruce. 2001. 'Productive and Unproductive Capital: A Mapping of the New Zealand System of National Accounts to Classical Economic Categories, 1972-1995.' Review of Political Economy 13(3): 309-327.</t>
-        </is>
-      </c>
+      <c r="B46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr"/>
-      <c r="B47" t="inlineStr"/>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>## Citation</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr"/>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+      <c r="B48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr"/>
-      <c r="B49" t="inlineStr"/>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Cronin, Bruce. 2001. 'Productive and Unproductive Capital: A Mapping of the New Zealand System of National Accounts to Classical Economic Categories, 1972-1995.' Review of Political Economy 13(3): 309-327.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr"/>
-      <c r="B50" t="inlineStr">
+      <c r="B50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr"/>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr"/>
+      <c r="B52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr"/>
+      <c r="B53" t="inlineStr">
         <is>
           <t>*Generated by anu-ingestion (re-authored from scratch).*</t>
         </is>
@@ -1080,7 +1105,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -1108,172 +1133,207 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>methodology_description</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>s/TV is the accumulation rate — surplus-value as a share of total value (TV = c + v + s). Total value is the classical concept of value produced by productive and trading sectors, derived by mapping NZSNA data to classical economic categories following Shaikh &amp; Tonak (1994). Surplus-value is total value minus constant capital (c) minus variable capital (v). The ratio measures the productive economy's capacity to generate surplus relative to total productive activity.</t>
+          <t>From a classical perspective, however, the conditions for renewed economic growth are not so apparent. Examining the relationship of surplus-value to total value reveals: A declining surplus in the period 1972 to 1983; A rise to 1989; Then a levelling out thereafter (see Table 2 and Fig. 10).</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Cronin_2001, body_text.md Section 3 (Deriving Classical Economic Categories); SUMMARY.md</t>
+          <t>Cronin 2001, Section 5 (Classical View)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>data_source</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Series ES1701-A: Digitized from Cronin (2001) Table 2, column S/TV, 1972-1995 (24 observations). Original table title: 'Rate of surplus-value and value composition of capital', Review of Political Economy 13(3), p. 15 (Table 2). Source CSV: Technical/Knowledge_Base/external_papers/international/2001_Cronin_New_Zealand/tables.csv. Values are decimal fractions (e.g., 34% = 0.34).</t>
+          <t>The conventional category of gross output increases faster than the classical concept of total value, particularly during the late 1980s and early 1990s, because of the growth of classically unproductive activity in the economy in this period (Fig. 13). The growth of unproductive activity can be seen in the relationship of total wages to variable capital, the latter growing more quickly, reflecting the growth of unproductive employment.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Cronin_2001, Table 2; tables.csv rows 27-52</t>
+          <t>Cronin 2001, Section 5 (Growth of Unproductive Activity)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>empirical_values</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Annual s/TV values (decimal): 1972=0.34, 1973=0.36, 1974=0.34, 1975=0.29, 1976=0.30, 1977=0.33, 1978=0.31, 1979=0.32, 1980=0.32, 1981=0.32, 1982=0.31, 1983=0.31, 1984=0.32, 1985=0.32, 1986=0.34, 1987=0.37, 1988=0.37, 1989=0.38, 1990=0.38, 1991=0.38, 1992=0.38, 1993=0.37, 1994=0.38, 1995=0.38.</t>
+          <t>Thus, the improvement in economic fundamentals emphasised by the neo-liberal reformers in New Zealand appears to arise from a short-term rise in the rate of surplus-value. The growth in unproductive activity throughout the 1980s and 90s gives an appearance of sustainable growth, but productive activity capable of generating surplus-value, and thus lagging indicators such as productivity and employment, remains weak.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Cronin_2001, Table 2; tables.csv</t>
+          <t>Cronin 2001, Section 6 (Conclusions)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>periodization</t>
+          <t>methodology_description</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Three distinct periods: (1) 1972-1983 profitability crisis — s/TV fell from 34% to 31%, reflecting a rising value composition of capital with stable exploitation rate; classic falling rate of profit conditions. (2) 1984-1989 neo-liberal recovery — s/TV rose from 32% to 38%, driven by a 37% jump in the rate of surplus-value as Rogernomics reforms intensified labor exploitation. (3) 1990-1995 stagnation — s/TV plateaued at 38% despite continued rise in s/v, because renewed rise in value composition of capital offset gains in exploitation.</t>
+          <t>s/TV is the accumulation rate — surplus-value as a share of total value (TV = c + v + s). Total value is the classical concept of value produced by productive and trading sectors, derived by mapping NZSNA data to classical economic categories following Shaikh &amp; Tonak (1994). Surplus-value is total value minus constant capital (c) minus variable capital (v). The ratio measures the productive economy's capacity to generate surplus relative to total productive activity.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Cronin_2001, body_text.md Section 5; SUMMARY.md</t>
+          <t>Cronin_2001, body_text.md Section 3 (Deriving Classical Economic Categories); SUMMARY.md</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>structural_break</t>
+          <t>data_source</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>The 1984 Rogernomics reforms (Roger Douglas, Labour government) are the key structural break. Post-1984, the expansion of unproductive activity (financial sector, trade, administration) increased the unproductive share of gross output relative to total value — visible in gross output growing faster than total value from the late 1980s onward. The s/TV ratio improvement 1984-1989 masks the underlying dynamic: gains were exploitation-driven, not productivity-driven, and the unproductive sector drained surplus from productive investment.</t>
+          <t>Series ES1701-A: Digitized from Cronin (2001) Table 2, column S/TV, 1972-1995 (24 observations). Original table title: 'Rate of surplus-value and value composition of capital', Review of Political Economy 13(3), p. 15 (Table 2). Source CSV: Technical/Knowledge_Base/external_papers/international/2001_Cronin_New_Zealand/tables.csv. Values are decimal fractions (e.g., 34% = 0.34).</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Cronin_2001, body_text.md Section 5 (Growth of Unproductive Activity); SUMMARY.md</t>
+          <t>Cronin_2001, Table 2; tables.csv rows 27-52</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>figure_context</t>
+          <t>empirical_values</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Cronin Fig 10: plots s/TV for 1972-1995, showing the three-period structure. Fig 12: compares accumulation rate (s/TV) with rate of surplus-value (s/v), showing close tracking until the 1984-87 divergence when unproductive activity growth decoupled the two ratios.</t>
+          <t>Annual s/TV values (decimal): 1972=0.34, 1973=0.36, 1974=0.34, 1975=0.29, 1976=0.30, 1977=0.33, 1978=0.31, 1979=0.32, 1980=0.32, 1981=0.32, 1982=0.31, 1983=0.31, 1984=0.32, 1985=0.32, 1986=0.34, 1987=0.37, 1988=0.37, 1989=0.38, 1990=0.38, 1991=0.38, 1992=0.38, 1993=0.37, 1994=0.38, 1995=0.38.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Cronin_2001, body_text.md Section 5</t>
+          <t>Cronin_2001, Table 2; tables.csv</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>caveat</t>
+          <t>periodization</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>s/TV is described by Cronin as the 'accumulation rate' — the share of total productive value available for accumulation. It differs from the conventional profit share because total value excludes unproductive activity. The conventional proxy (operating surplus / employee compensation) understates s/v by a factor of roughly 3-4 and shows little variation, while classical s/TV rises meaningfully from 1984.</t>
+          <t>Three distinct periods: (1) 1972-1983 profitability crisis — s/TV fell from 34% to 31%, reflecting a rising value composition of capital with stable exploitation rate; classic falling rate of profit conditions. (2) 1984-1989 neo-liberal recovery — s/TV rose from 32% to 38%, driven by a 37% jump in the rate of surplus-value as Rogernomics reforms intensified labor exploitation. (3) 1990-1995 stagnation — s/TV plateaued at 38% despite continued rise in s/v, because renewed rise in value composition of capital offset gains in exploitation.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Cronin_2001, body_text.md Section 4 (Conventional Proxy Measures); SUMMARY.md</t>
-        </is>
-      </c>
-    </row>
-    <row r="9"/>
+          <t>Cronin_2001, body_text.md Section 5; SUMMARY.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>structural_break</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>The 1984 Rogernomics reforms (Roger Douglas, Labour government) are the key structural break. Post-1984, the expansion of unproductive activity (financial sector, trade, administration) increased the unproductive share of gross output relative to total value — visible in gross output growing faster than total value from the late 1980s onward. The s/TV ratio improvement 1984-1989 masks the underlying dynamic: gains were exploitation-driven, not productivity-driven, and the unproductive sector drained surplus from productive investment.</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Cronin_2001, body_text.md Section 5 (Growth of Unproductive Activity); SUMMARY.md</t>
+        </is>
+      </c>
+    </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>figure_context</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Cronin Fig 10: plots s/TV for 1972-1995, showing the three-period structure. Fig 12: compares accumulation rate (s/TV) with rate of surplus-value (s/v), showing close tracking until the 1984-87 divergence when unproductive activity growth decoupled the two ratios.</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Cronin_2001, body_text.md Section 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>caveat</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>s/TV is described by Cronin as the 'accumulation rate' — the share of total productive value available for accumulation. It differs from the conventional profit share because total value excludes unproductive activity. The conventional proxy (operating surplus / employee compensation) understates s/v by a factor of roughly 3-4 and shows little variation, while classical s/TV rises meaningfully from 1984.</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Cronin_2001, body_text.md Section 4 (Conventional Proxy Measures); SUMMARY.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>methodology_summary</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>s/TV (productive capital share / accumulation rate) is directly digitized from Cronin (2001) Table 2. Derived from NZSNA mapped to classical categories via Shaikh-Tonak methodology applied to 25 NZ production groups, 1972-1995. No extension beyond 1995.</t>
         </is>
       </c>
     </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="14"/>
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>known_issues:</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr"/>
-      <c r="B13" t="inlineStr">
+    <row r="16">
+      <c r="A16" t="inlineStr"/>
+      <c r="B16" t="inlineStr">
         <is>
           <t>No post-1995 extension available from this source</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr"/>
-      <c r="B14" t="inlineStr">
+    <row r="17">
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" t="inlineStr">
         <is>
           <t>Non-capitalist production (small self-employed and non-profit sector) assumed negligible and included as capitalist — Cronin notes data insufficient to isolate</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr"/>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Some inter-industry years interpolated using annual NZSNA data rather than full IO tables</t>
-        </is>
-      </c>
-    </row>
-    <row r="16"/>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>cross_references:</t>
         </is>
       </c>
     </row>
@@ -1281,53 +1341,69 @@
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
+          <t>Some inter-industry years interpolated using annual NZSNA data rather than full IO tables</t>
+        </is>
+      </c>
+    </row>
+    <row r="19"/>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>cross_references:</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr"/>
+      <c r="B21" t="inlineStr">
+        <is>
           <t>ES1702</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr">
+    <row r="22">
+      <c r="A22" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
         <is>
           <t>ES1703</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr">
+    <row r="23">
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="inlineStr">
         <is>
           <t>ES1704</t>
         </is>
       </c>
     </row>
-    <row r="21"/>
-    <row r="22">
-      <c r="A22" t="inlineStr">
+    <row r="24"/>
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>citations:</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+    <row r="26">
+      <c r="A26" t="inlineStr">
         <is>
           <t>Cronin_2001</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>Cronin, Bruce. 2001. 'Productive and Unproductive Capital: A mapping of the New Zealand system of national accounts to classical economic categories, 1972-95.' Review of Political Economy 13(3): 309-327. https://doi.org/10.1080/09538250120055168</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
+    <row r="27">
+      <c r="A27" t="inlineStr">
         <is>
           <t>ST_1994</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>Shaikh, Anwar, and E. Ahmet Tonak. 1994. Measuring the Wealth of Nations: The Political Economy of National Accounts. Cambridge University Press.</t>
         </is>
@@ -1344,7 +1420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1407,7 +1483,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>null — series does not extend beyond book period</t>
+          <t>null - series does not extend beyond book period</t>
         </is>
       </c>
     </row>
@@ -1453,6 +1529,42 @@
       <c r="B9" t="inlineStr">
         <is>
           <t>share_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>tolerance_class</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>share_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>tolerance_rel</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>tolerance_abs</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>0.02</t>
         </is>
       </c>
     </row>
